--- a/public/plantilla-precios.xlsx
+++ b/public/plantilla-precios.xlsx
@@ -397,10 +397,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -410,6 +411,9 @@
       <c r="B1" t="str">
         <v>precio</v>
       </c>
+      <c r="C1" t="str">
+        <v>opcion_facturacion</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -418,6 +422,9 @@
       <c r="B2">
         <v>2755.5</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -426,6 +433,9 @@
       <c r="B3">
         <v>33800.9</v>
       </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -434,10 +444,13 @@
       <c r="B4">
         <v>16200</v>
       </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>